--- a/series_data/night-archive/series_log.xlsx
+++ b/series_data/night-archive/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -830,6 +830,120 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep01/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:51</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/85b58e0354063aba40d3c34701349172_1783111723.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projects\Youtube\output\series\night-archive\episodes\ep01\shots\shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-03 13:53</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b94f14ac5f8ac6e9c95841103b82b93a_1783112002.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>C:\Users\ihsan\Desktop\Antigravity\Projects\Youtube\output\series\night-archive\episodes\ep01\shots\shot_06.mp4</t>
         </is>
       </c>
     </row>

--- a/series_data/night-archive/series_log.xlsx
+++ b/series_data/night-archive/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -947,6 +947,356 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-05 19:54</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/425c817b8d591f3a10ad71253b49e3c2_1783281223.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-05 19:59</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f49675f2412910a6e48b65f167123f5c_1783281529.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-05 20:03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a7b8463bfbca27e74f24e374db7c31c5_1783281748.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-05 20:07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c82beb8c3599cf7b6314c4726bef363c_1783282019.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep02/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-05 20:11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4772c336f77ffc32d30df75ae646a1f9_1783282238.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep02/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-05 20:14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e6a86df124cae8f5a9d959d98276798b_1783282405.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep02/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/night-archive/series_log.xlsx
+++ b/series_data/night-archive/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1297,6 +1297,356 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:27</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/15aa67e530a2ebe33b720842823d8625_1783369598.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:29</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6440618987011371f67aaef26fa1641a_1783369739.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/547498a1e07910979272f995e189d8bc_1783369878.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:35</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6119b67614ff5cbe5d401b71d18e5bcb_1783370089.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:37</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5b1e50c8d8359d417f91fb27695de452_1783370236.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep03/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:40</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fe50be471afd6eb56e1a66374a6eeaa2_1783370415.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep03/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/night-archive/series_log.xlsx
+++ b/series_data/night-archive/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1647,6 +1647,356 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-07 20:30</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/de36dd2029f17c9398f5e05e60657fad_1783456190.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-07 20:37</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d67766e58d9682ef1b845ad87085b186_1783456589.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-07 20:51</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9a0cf3cf947a80f463b6f531c925a39c_1783457482.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-07 20:54</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4bc67b780d5855f441459b2801d7b890_1783457639.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-07 20:58</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5bb16fd97e6d616b9b2e7cace27423c5_1783457853.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep04/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-07 21:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cc6a2fc4258278cf5197778a4bf7ebbf_1783458013.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/night-archive/episodes/ep04/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
